--- a/KURIKULUM2026_REVISI/034_SEMBILAN_BENTUK_MBKM_DAN_REKOGNISI.xlsx
+++ b/KURIKULUM2026_REVISI/034_SEMBILAN_BENTUK_MBKM_DAN_REKOGNISI.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Konversi ke `STI-625` Smart City (2) + PKL + MK pengabdian</t>
+          <t>Konversi ke `STI-727` Smart City (2) + PKL + MK pengabdian</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Peminatan MK-2 &amp; MK-3 (6), `STI-624` Integrasi AI (3), `STI-627` Platform Eng (3), `STI-625` Smart City (2), `STI-626` Deep Learning (+P) (3), `FST-611` Metopel (2)</t>
+          <t>Peminatan MK-2 &amp; MK-3 (6), `STI-726` Integrasi AI (3), `STI-727` Platform Eng (3), `STI-727` Smart City (2), `STI-726` Deep Learning (+P) (3), `FST-611` Metopel (2)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
